--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_adv.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_adv.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="god" sheetId="1" r:id="rId3"/>
-    <sheet name="general" sheetId="2" r:id="rId4"/>
+    <sheet name="god" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="general" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="118">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -454,84 +454,6 @@
   <si>
     <t xml:space="preserve">What?</t>
   </si>
-  <si>
-    <t xml:space="preserve">- 你走近祭坛，想起了关于众神的传说。
-&lt;color=olive&gt;《#god_name》&lt;/color&gt;
-#god_desc
-#god_benefit</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">信仰#god_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">离去</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神圣的声音在你的脑海里响起。
-「#godtalk_worship」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">结婚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">西埃尔历#1年#2，#4在#3向#5求婚了。
-两人静静地牵着手，在这里为永远的爱献上誓言。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在此约定终生</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不眠的星辰啊，流转的明月啊。今夜，请见证这对新人的启程，祝福这幸运的日子吧。
-﻿
-向夜空奉上花束，为明日献上亲吻，不久之后就会化作闪耀黄金光辉的果实。
-﻿
-当月光洒向地面的时候，在永远的誓言中，两人将会结为密不可分的连理。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#pc_full。
-你愿意让#tg作为你一生的伴侣，无论是在喜悦的清晨，还是含泪的夜晚，都永远不放开那双手，发誓永远相伴吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我愿意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不愿意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#tg。
-你愿意将#pc_full作为唯一的伴侣，无论是面对命运的暴风雨，还是沉浸于寂静的安眠，都将那颗心托付给对方，发誓一起走下去吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我愿意。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在星辰的见证下，两人就此结为连理。让幸运女神祝福你们…！ 
-来吧……献上誓约之吻。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">誓约之吻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">爽一爽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">羞涩地沉默</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逃走</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（#tg羞涩地微笑着，静静地与你重叠起双唇）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（#tg轻轻一笑，温柔地将嘴唇贴近你）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…诶？</t>
-  </si>
 </sst>
 </file>
 
@@ -552,19 +474,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -596,7 +518,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -605,62 +527,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -674,13 +596,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -856,24 +778,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW442"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -908,13 +830,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -922,7 +844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
@@ -930,7 +852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -938,7 +860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
@@ -946,7 +868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
@@ -954,7 +876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -962,7 +884,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
@@ -970,7 +892,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,7 +900,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
@@ -986,7 +908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
@@ -994,7 +916,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1002,7 +924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1010,7 +932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1018,7 +940,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1026,7 +948,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1034,7 +956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1042,7 +964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1050,7 +972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
@@ -1058,7 +980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1066,7 +988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1074,17 +996,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1092,7 +1014,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="12.8">
+    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1355,11 +1277,11 @@
       <c r="IV29" s="1"/>
       <c r="IW29" s="1"/>
     </row>
-    <row r="30" ht="74.6">
+    <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -1368,9 +1290,7 @@
       <c r="J30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -1618,14 +1538,14 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -1634,18 +1554,15 @@
       <c r="J31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K31" t="s">
-        <v>120</v>
-      </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -1654,20 +1571,17 @@
       <c r="J32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K32" t="s">
-        <v>121</v>
-      </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1677,18 +1591,18 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" ht="32.8">
+    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I37" s="4" t="s">
@@ -1697,19 +1611,16 @@
       <c r="J37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K37" t="s">
-        <v>122</v>
-      </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -1958,7 +1869,7 @@
       <c r="IV40" s="1"/>
       <c r="IW40" s="1"/>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="1"/>
@@ -2209,23 +2120,23 @@
       <c r="IV44" s="1"/>
       <c r="IW44" s="1"/>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="64" s="3" customFormat="1" ht="12.8">
+    <row r="64" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2484,7 +2395,7 @@
       <c r="IV64" s="1"/>
       <c r="IW64" s="1"/>
     </row>
-    <row r="66" ht="12.8">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -2733,7 +2644,7 @@
       <c r="IV66" s="1"/>
       <c r="IW66" s="1"/>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -2982,7 +2893,7 @@
       <c r="IV67" s="1"/>
       <c r="IW67" s="1"/>
     </row>
-    <row r="68" s="5" customFormat="1" ht="12.8">
+    <row r="68" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3241,7 +3152,7 @@
       <c r="IV68" s="1"/>
       <c r="IW68" s="1"/>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -3490,7 +3401,7 @@
       <c r="IV70" s="1"/>
       <c r="IW70" s="1"/>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3739,7 +3650,7 @@
       <c r="IV71" s="1"/>
       <c r="IW71" s="1"/>
     </row>
-    <row r="85" s="3" customFormat="1" ht="12.8">
+    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3998,7 +3909,7 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -4247,7 +4158,7 @@
       <c r="IV87" s="1"/>
       <c r="IW87" s="1"/>
     </row>
-    <row r="88" ht="12.8">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -4496,7 +4407,7 @@
       <c r="IV88" s="1"/>
       <c r="IW88" s="1"/>
     </row>
-    <row r="89" s="5" customFormat="1" ht="12.8">
+    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4755,7 +4666,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="91" ht="12.8">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
@@ -5004,7 +4915,7 @@
       <c r="IV91" s="1"/>
       <c r="IW91" s="1"/>
     </row>
-    <row r="92" ht="12.8">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
@@ -5253,7 +5164,7 @@
       <c r="IV92" s="1"/>
       <c r="IW92" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="1" ht="12.8">
+    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5512,7 +5423,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="101" ht="12.8">
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
@@ -5761,7 +5672,7 @@
       <c r="IV101" s="1"/>
       <c r="IW101" s="1"/>
     </row>
-    <row r="102" ht="12.8">
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
@@ -6010,7 +5921,7 @@
       <c r="IV102" s="1"/>
       <c r="IW102" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="1" ht="12.8">
+    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -6269,7 +6180,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="1" ht="12.8">
+    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -6528,7 +6439,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="1" ht="12.8">
+    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -6787,7 +6698,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="120" ht="12.8">
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -7036,7 +6947,7 @@
       <c r="IV120" s="1"/>
       <c r="IW120" s="1"/>
     </row>
-    <row r="121" ht="12.8">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
@@ -7285,7 +7196,7 @@
       <c r="IV121" s="1"/>
       <c r="IW121" s="1"/>
     </row>
-    <row r="122" ht="12.8">
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
@@ -7534,7 +7445,7 @@
       <c r="IV122" s="1"/>
       <c r="IW122" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="1" ht="12.8">
+    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7793,7 +7704,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="1" ht="12.8">
+    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -8052,7 +7963,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="1" ht="12.8">
+    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -8311,7 +8222,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="1" ht="12.8">
+    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8570,7 +8481,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="1" ht="12.8">
+    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8829,7 +8740,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="131" ht="12.8">
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
@@ -9078,7 +8989,7 @@
       <c r="IV131" s="1"/>
       <c r="IW131" s="1"/>
     </row>
-    <row r="132" ht="12.8">
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
@@ -9327,7 +9238,7 @@
       <c r="IV132" s="1"/>
       <c r="IW132" s="1"/>
     </row>
-    <row r="133" ht="12.8">
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
@@ -9576,7 +9487,7 @@
       <c r="IV133" s="1"/>
       <c r="IW133" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="1" ht="12.8">
+    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -9835,7 +9746,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="159" ht="12.8">
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
@@ -10084,7 +9995,7 @@
       <c r="IV159" s="1"/>
       <c r="IW159" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="1" ht="12.8">
+    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -10343,7 +10254,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="1" ht="12.8">
+    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -10602,7 +10513,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="162" ht="12.8">
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
@@ -10851,7 +10762,7 @@
       <c r="IV162" s="1"/>
       <c r="IW162" s="1"/>
     </row>
-    <row r="163" ht="12.8">
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
@@ -11100,7 +11011,7 @@
       <c r="IV163" s="1"/>
       <c r="IW163" s="1"/>
     </row>
-    <row r="164" ht="12.8">
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K164" s="1"/>
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
@@ -11349,7 +11260,7 @@
       <c r="IV164" s="1"/>
       <c r="IW164" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="1" ht="12.8">
+    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -11608,7 +11519,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="238" ht="12.8">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
@@ -11857,7 +11768,7 @@
       <c r="IV238" s="1"/>
       <c r="IW238" s="1"/>
     </row>
-    <row r="239" ht="12.8">
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
@@ -12106,7 +12017,7 @@
       <c r="IV239" s="1"/>
       <c r="IW239" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="1" ht="12.8">
+    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -12365,7 +12276,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="242" ht="12.8">
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
@@ -12614,7 +12525,7 @@
       <c r="IV242" s="1"/>
       <c r="IW242" s="1"/>
     </row>
-    <row r="243" ht="12.8">
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
@@ -12863,7 +12774,7 @@
       <c r="IV243" s="1"/>
       <c r="IW243" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="1" ht="12.8">
+    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -13122,7 +13033,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="274" ht="12.8">
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
@@ -13371,7 +13282,7 @@
       <c r="IV274" s="1"/>
       <c r="IW274" s="1"/>
     </row>
-    <row r="275" ht="12.8">
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
@@ -13620,7 +13531,7 @@
       <c r="IV275" s="1"/>
       <c r="IW275" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="1" ht="12.8">
+    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -13879,7 +13790,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="1" ht="12.8">
+    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -14138,7 +14049,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="288" ht="12.8">
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
@@ -14387,7 +14298,7 @@
       <c r="IV288" s="1"/>
       <c r="IW288" s="1"/>
     </row>
-    <row r="289" ht="12.8">
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K289" s="1"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
@@ -14636,7 +14547,7 @@
       <c r="IV289" s="1"/>
       <c r="IW289" s="1"/>
     </row>
-    <row r="290" ht="12.8">
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
@@ -14885,7 +14796,7 @@
       <c r="IV290" s="1"/>
       <c r="IW290" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="1" ht="12.8">
+    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -15144,7 +15055,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="302" ht="12.8">
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
@@ -15393,7 +15304,7 @@
       <c r="IV302" s="1"/>
       <c r="IW302" s="1"/>
     </row>
-    <row r="303" ht="12.8">
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
@@ -15642,7 +15553,7 @@
       <c r="IV303" s="1"/>
       <c r="IW303" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="1" ht="12.8">
+    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -15901,7 +15812,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="308" ht="12.8">
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
@@ -16150,7 +16061,7 @@
       <c r="IV308" s="1"/>
       <c r="IW308" s="1"/>
     </row>
-    <row r="309" ht="12.8">
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
@@ -16399,7 +16310,7 @@
       <c r="IV309" s="1"/>
       <c r="IW309" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="1" ht="12.8">
+    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -16658,7 +16569,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="315" ht="12.8">
+    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
@@ -16907,7 +16818,7 @@
       <c r="IV315" s="1"/>
       <c r="IW315" s="1"/>
     </row>
-    <row r="316" ht="12.8">
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
@@ -17156,7 +17067,7 @@
       <c r="IV316" s="1"/>
       <c r="IW316" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="1" ht="12.8">
+    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -17415,7 +17326,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="339" ht="12.8">
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
@@ -17664,7 +17575,7 @@
       <c r="IV339" s="1"/>
       <c r="IW339" s="1"/>
     </row>
-    <row r="340" ht="12.8">
+    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
@@ -17913,7 +17824,7 @@
       <c r="IV340" s="1"/>
       <c r="IW340" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="1" ht="12.8">
+    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -18172,7 +18083,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="350" ht="12.8">
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K350" s="1"/>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
@@ -18421,7 +18332,7 @@
       <c r="IV350" s="1"/>
       <c r="IW350" s="1"/>
     </row>
-    <row r="351" ht="12.8">
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K351" s="1"/>
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
@@ -18670,7 +18581,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="1" ht="12.8">
+    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -18929,7 +18840,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="1" ht="12.8">
+    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -19188,7 +19099,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="356" ht="12.8">
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K356" s="1"/>
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
@@ -19437,7 +19348,7 @@
       <c r="IV356" s="1"/>
       <c r="IW356" s="1"/>
     </row>
-    <row r="357" ht="12.8">
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K357" s="1"/>
       <c r="L357" s="1"/>
       <c r="M357" s="1"/>
@@ -19686,7 +19597,7 @@
       <c r="IV357" s="1"/>
       <c r="IW357" s="1"/>
     </row>
-    <row r="358" ht="12.8">
+    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K358" s="1"/>
       <c r="L358" s="1"/>
       <c r="M358" s="1"/>
@@ -19935,7 +19846,7 @@
       <c r="IV358" s="1"/>
       <c r="IW358" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="1" ht="12.8">
+    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -20194,7 +20105,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="368" ht="12.8">
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K368" s="1"/>
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
@@ -20443,7 +20354,7 @@
       <c r="IV368" s="1"/>
       <c r="IW368" s="1"/>
     </row>
-    <row r="369" ht="12.8">
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K369" s="1"/>
       <c r="L369" s="1"/>
       <c r="M369" s="1"/>
@@ -20692,7 +20603,7 @@
       <c r="IV369" s="1"/>
       <c r="IW369" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="1" ht="12.8">
+    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -20951,7 +20862,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="413" ht="12.8">
+    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K413" s="1"/>
       <c r="L413" s="1"/>
       <c r="M413" s="1"/>
@@ -21200,7 +21111,7 @@
       <c r="IV413" s="1"/>
       <c r="IW413" s="1"/>
     </row>
-    <row r="414" ht="12.8">
+    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K414" s="1"/>
       <c r="L414" s="1"/>
       <c r="M414" s="1"/>
@@ -21449,7 +21360,7 @@
       <c r="IV414" s="1"/>
       <c r="IW414" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="1" ht="12.8">
+    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -21708,7 +21619,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="1" ht="12.8">
+    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -21967,7 +21878,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="417" ht="12.8">
+    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K417" s="1"/>
       <c r="L417" s="1"/>
       <c r="M417" s="1"/>
@@ -22216,7 +22127,7 @@
       <c r="IV417" s="1"/>
       <c r="IW417" s="1"/>
     </row>
-    <row r="418" ht="12.8">
+    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K418" s="1"/>
       <c r="L418" s="1"/>
       <c r="M418" s="1"/>
@@ -22465,7 +22376,7 @@
       <c r="IV418" s="1"/>
       <c r="IW418" s="1"/>
     </row>
-    <row r="419" ht="12.8">
+    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K419" s="1"/>
       <c r="L419" s="1"/>
       <c r="M419" s="1"/>
@@ -22714,7 +22625,7 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="1" ht="12.8">
+    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -22973,7 +22884,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="1" ht="12.8">
+    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -23232,7 +23143,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="431" ht="12.8">
+    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K431" s="1"/>
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
@@ -23481,7 +23392,7 @@
       <c r="IV431" s="1"/>
       <c r="IW431" s="1"/>
     </row>
-    <row r="432" ht="12.8">
+    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K432" s="1"/>
       <c r="L432" s="1"/>
       <c r="M432" s="1"/>
@@ -23730,7 +23641,7 @@
       <c r="IV432" s="1"/>
       <c r="IW432" s="1"/>
     </row>
-    <row r="433" ht="12.8">
+    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K433" s="1"/>
       <c r="L433" s="1"/>
       <c r="M433" s="1"/>
@@ -23979,7 +23890,7 @@
       <c r="IV433" s="1"/>
       <c r="IW433" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="1" ht="12.8">
+    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -24238,7 +24149,7 @@
       <c r="IV439" s="1"/>
       <c r="IW439" s="1"/>
     </row>
-    <row r="441" ht="12.8">
+    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K441" s="1"/>
       <c r="L441" s="1"/>
       <c r="M441" s="1"/>
@@ -24487,7 +24398,7 @@
       <c r="IV441" s="1"/>
       <c r="IW441" s="1"/>
     </row>
-    <row r="442" ht="12.8">
+    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K442" s="1"/>
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
@@ -24738,12 +24649,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -24751,24 +24662,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW439"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24803,13 +24714,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -24817,14 +24728,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -24833,11 +24744,8 @@
       <c r="J6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K6" t="s">
-        <v>123</v>
-      </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -24845,12 +24753,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -25099,20 +25007,20 @@
       <c r="IV10" s="1"/>
       <c r="IW10" s="1"/>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>37</v>
       </c>
@@ -25120,11 +25028,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="n">
         <v>123</v>
       </c>
       <c r="I15" s="4"/>
@@ -25377,11 +25285,11 @@
       <c r="IV15" s="1"/>
       <c r="IW15" s="1"/>
     </row>
-    <row r="16" ht="43.25">
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
@@ -25390,9 +25298,7 @@
       <c r="J16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>124</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -25640,7 +25546,7 @@
       <c r="IV16" s="1"/>
       <c r="IW16" s="1"/>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>61</v>
       </c>
@@ -25650,7 +25556,7 @@
       <c r="F17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -25659,22 +25565,19 @@
       <c r="J17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K17" t="s">
-        <v>125</v>
-      </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>61</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>64</v>
       </c>
@@ -25684,24 +25587,24 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="1" t="s">
         <v>66</v>
       </c>
@@ -25709,20 +25612,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="1" t="s">
         <v>64</v>
       </c>
@@ -25730,7 +25633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D30" s="1" t="s">
         <v>71</v>
       </c>
@@ -25738,35 +25641,35 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="1" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="85.05">
+    <row r="34" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F34" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I34" s="4" t="s">
@@ -25775,11 +25678,8 @@
       <c r="J34" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K34" t="s">
-        <v>126</v>
-      </c>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="1" t="s">
         <v>73</v>
       </c>
@@ -25787,11 +25687,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" ht="53.7">
+    <row r="36" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I36" s="4" t="s">
@@ -25800,18 +25700,15 @@
       <c r="J36" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="K36" t="s">
-        <v>127</v>
-      </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -25820,18 +25717,15 @@
       <c r="J37" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K37" t="s">
-        <v>128</v>
-      </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -25840,17 +25734,14 @@
       <c r="J38" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K38" t="s">
-        <v>129</v>
-      </c>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" ht="12.8">
-      <c r="H42" s="1">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -25859,19 +25750,16 @@
       <c r="J42" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K42" t="s">
-        <v>86</v>
-      </c>
     </row>
-    <row r="43" ht="12.8">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D43" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="1" t="s">
         <v>64</v>
       </c>
@@ -25879,17 +25767,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="1" t="s">
         <v>73</v>
       </c>
@@ -25897,11 +25785,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51" ht="53.7">
+    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F51" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -25910,11 +25798,8 @@
       <c r="J51" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K51" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="52" ht="12.8">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="1" t="s">
         <v>73</v>
       </c>
@@ -25922,8 +25807,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" ht="12.8">
-      <c r="H53" s="1">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -25932,11 +25817,8 @@
       <c r="J53" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K53" t="s">
-        <v>131</v>
-      </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D54" s="1" t="s">
         <v>73</v>
       </c>
@@ -25944,11 +25826,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" ht="43.25">
+    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F55" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I55" s="4" t="s">
@@ -25957,18 +25839,15 @@
       <c r="J55" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K55" t="s">
-        <v>132</v>
-      </c>
     </row>
-    <row r="56" ht="12.8">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -25977,18 +25856,15 @@
       <c r="J56" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K56" t="s">
-        <v>133</v>
-      </c>
     </row>
-    <row r="57" ht="12.8">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -25997,18 +25873,15 @@
       <c r="J57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K57" t="s">
-        <v>134</v>
-      </c>
     </row>
-    <row r="58" ht="12.8">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -26017,18 +25890,15 @@
       <c r="J58" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K58" t="s">
-        <v>135</v>
-      </c>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -26037,11 +25907,8 @@
       <c r="J59" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K59" t="s">
-        <v>136</v>
-      </c>
     </row>
-    <row r="61" s="3" customFormat="1" ht="12.8">
+    <row r="61" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
         <v>94</v>
       </c>
@@ -26302,8 +26169,8 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" ht="12.8">
-      <c r="H62" s="1">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I62" s="7" t="s">
@@ -26312,16 +26179,13 @@
       <c r="J62" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K62" t="s">
-        <v>137</v>
-      </c>
     </row>
-    <row r="63" ht="12.8">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="65" s="5" customFormat="1" ht="12.8">
+    <row r="65" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>100</v>
       </c>
@@ -26582,8 +26446,8 @@
       <c r="IV65" s="1"/>
       <c r="IW65" s="1"/>
     </row>
-    <row r="66" ht="12.8">
-      <c r="H66" s="1">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I66" s="7" t="s">
@@ -26592,21 +26456,18 @@
       <c r="J66" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K66" t="s">
-        <v>138</v>
-      </c>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D71" s="1" t="s">
         <v>35</v>
       </c>
@@ -26614,16 +26475,16 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" ht="12.8">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D72" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" ht="12.8">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="1" t="s">
         <v>64</v>
       </c>
@@ -26632,16 +26493,16 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" ht="12.8">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D74" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" ht="12.8">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D75" s="1" t="s">
         <v>64</v>
       </c>
@@ -26650,17 +26511,17 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" ht="12.8">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="79" ht="12.8">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="80" ht="12.8">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="1" t="s">
         <v>114</v>
       </c>
@@ -26668,17 +26529,17 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" ht="12.8">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="84" ht="12.8">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="85" s="3" customFormat="1" ht="12.8">
+    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -26686,7 +26547,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1">
+      <c r="H85" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -26695,9 +26556,7 @@
       <c r="J85" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
@@ -26945,12 +26804,12 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="86" ht="12.8">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="89" s="5" customFormat="1" ht="12.8">
+    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -27209,7 +27068,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="1" ht="12.8">
+    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -27468,7 +27327,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="1" ht="12.8">
+    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -27727,7 +27586,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="1" ht="12.8">
+    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -27986,7 +27845,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="1" ht="12.8">
+    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -28245,7 +28104,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="1" ht="12.8">
+    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -28504,7 +28363,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="1" ht="12.8">
+    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -28763,7 +28622,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="1" ht="12.8">
+    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -29022,7 +28881,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="1" ht="12.8">
+    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -29281,7 +29140,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="1" ht="12.8">
+    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -29540,7 +29399,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="1" ht="12.8">
+    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -29799,7 +29658,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="1" ht="12.8">
+    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -30058,7 +29917,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="1" ht="12.8">
+    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -30317,7 +30176,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="1" ht="12.8">
+    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -30576,7 +30435,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="1" ht="12.8">
+    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -30835,7 +30694,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="1" ht="12.8">
+    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -31094,7 +30953,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="1" ht="12.8">
+    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -31353,7 +31212,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="1" ht="12.8">
+    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -31612,7 +31471,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="1" ht="12.8">
+    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -31871,7 +31730,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="1" ht="12.8">
+    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -32130,7 +31989,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="1" ht="12.8">
+    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -32389,7 +32248,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="1" ht="12.8">
+    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -32648,7 +32507,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="1" ht="12.8">
+    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -32907,7 +32766,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="1" ht="12.8">
+    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -33166,7 +33025,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="1" ht="12.8">
+    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -33425,7 +33284,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="1" ht="12.8">
+    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -33684,7 +33543,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="1" ht="12.8">
+    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -33943,7 +33802,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="1" ht="12.8">
+    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -34202,7 +34061,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="1" ht="12.8">
+    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -34461,7 +34320,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="1" ht="12.8">
+    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -34720,7 +34579,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="1" ht="12.8">
+    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -34979,7 +34838,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="1" ht="12.8">
+    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -35240,21 +35099,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H11 H14 H72:H1048576 H36:H70 H24:H34">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H23 H12:H13">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H71">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_adv.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_adv.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="god" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="general" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="god" sheetId="1" r:id="rId3"/>
+    <sheet name="general" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="140">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -454,6 +454,84 @@
   <si>
     <t xml:space="preserve">What?</t>
   </si>
+  <si>
+    <t xml:space="preserve">- 你走近祭坛，想起了关于众神的传说。
+&lt;color=olive&gt;《#god_name》&lt;/color&gt;
+#god_desc
+#god_benefit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">信仰#god_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">离去</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神圣的声音在你的脑海里响起。
+「#godtalk_worship」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结婚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">西埃尔历#1年#2，#4在#3向#5求婚了。
+两人静静地牵着手，在这里为永远的爱献上誓言。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在此约定终生</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不眠的星辰啊，流转的明月啊。今夜，请见证这对新人的启程，祝福这幸运的日子吧。
+﻿
+向夜空奉上花束，为明日献上亲吻，不久之后就会化作闪耀黄金光辉的果实。
+﻿
+当月光洒向地面的时候，在永远的誓言中，两人将会结为密不可分的连理。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#pc_full。
+你愿意让#tg作为你一生的伴侣，无论是在喜悦的清晨，还是含泪的夜晚，都永远不放开那双手，发誓永远相伴吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我愿意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不愿意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#tg。
+你愿意将#pc_full作为唯一的伴侣，无论是面对命运的暴风雨，还是沉浸于寂静的安眠，都将那颗心托付给对方，发誓一起走下去吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我愿意。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在星辰的见证下，两人就此结为连理。让幸运女神祝福你们…！ 
+来吧……献上誓约之吻。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">誓约之吻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">爽一爽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">羞涩地沉默</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逃走</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（#tg羞涩地微笑着，静静地与你重叠起双唇）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（#tg轻轻一笑，温柔地将嘴唇贴近你）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…诶？</t>
+  </si>
 </sst>
 </file>
 
@@ -474,19 +552,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -518,7 +596,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -527,62 +605,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -596,13 +674,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -778,24 +856,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IW442"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
+    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -830,13 +908,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -844,7 +922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
@@ -852,7 +930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -860,7 +938,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
@@ -868,7 +946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
@@ -876,7 +954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
@@ -884,7 +962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
@@ -892,7 +970,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
@@ -900,7 +978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
@@ -908,7 +986,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
@@ -916,7 +994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
@@ -924,7 +1002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
@@ -932,7 +1010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
@@ -940,7 +1018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="D18" s="1" t="s">
         <v>13</v>
       </c>
@@ -948,7 +1026,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>13</v>
       </c>
@@ -956,7 +1034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>13</v>
       </c>
@@ -964,7 +1042,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>13</v>
       </c>
@@ -972,7 +1050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
@@ -980,7 +1058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,7 +1066,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
@@ -996,17 +1074,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
         <v>35</v>
       </c>
@@ -1014,7 +1092,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="3" customFormat="1" ht="12.8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1277,11 +1355,11 @@
       <c r="IV29" s="1"/>
       <c r="IW29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="74.6">
       <c r="F30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="1">
         <v>1</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -1290,7 +1368,9 @@
       <c r="J30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -1538,14 +1618,14 @@
       <c r="IV30" s="1"/>
       <c r="IW30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="B31" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="1">
         <v>2</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -1554,15 +1634,18 @@
       <c r="J31" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="K31" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="1">
         <v>3</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -1571,17 +1654,20 @@
       <c r="J32" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="K32" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="D33" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1591,18 +1677,18 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="D36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="32.8">
       <c r="F37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="1">
         <v>4</v>
       </c>
       <c r="I37" s="4" t="s">
@@ -1611,16 +1697,19 @@
       <c r="J37" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="K37" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -1869,7 +1958,7 @@
       <c r="IV40" s="1"/>
       <c r="IW40" s="1"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="1"/>
@@ -2120,23 +2209,23 @@
       <c r="IV44" s="1"/>
       <c r="IW44" s="1"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="64" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="3" customFormat="1" ht="12.8">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2395,7 +2484,7 @@
       <c r="IV64" s="1"/>
       <c r="IW64" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="12.8">
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -2644,7 +2733,7 @@
       <c r="IV66" s="1"/>
       <c r="IW66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -2893,7 +2982,7 @@
       <c r="IV67" s="1"/>
       <c r="IW67" s="1"/>
     </row>
-    <row r="68" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="5" customFormat="1" ht="12.8">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3152,7 +3241,7 @@
       <c r="IV68" s="1"/>
       <c r="IW68" s="1"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -3401,7 +3490,7 @@
       <c r="IV70" s="1"/>
       <c r="IW70" s="1"/>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3650,7 +3739,7 @@
       <c r="IV71" s="1"/>
       <c r="IW71" s="1"/>
     </row>
-    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="3" customFormat="1" ht="12.8">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3909,7 +3998,7 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -4158,7 +4247,7 @@
       <c r="IV87" s="1"/>
       <c r="IW87" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="12.8">
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -4407,7 +4496,7 @@
       <c r="IV88" s="1"/>
       <c r="IW88" s="1"/>
     </row>
-    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="5" customFormat="1" ht="12.8">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4666,7 +4755,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.8">
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
@@ -4915,7 +5004,7 @@
       <c r="IV91" s="1"/>
       <c r="IW91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.8">
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
@@ -5164,7 +5253,7 @@
       <c r="IV92" s="1"/>
       <c r="IW92" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" s="5" customFormat="1" ht="12.8">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5423,7 +5512,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="12.8">
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
@@ -5672,7 +5761,7 @@
       <c r="IV101" s="1"/>
       <c r="IW101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" ht="12.8">
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
@@ -5921,7 +6010,7 @@
       <c r="IV102" s="1"/>
       <c r="IW102" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="3" customFormat="1" ht="12.8">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -6180,7 +6269,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="3" customFormat="1" ht="12.8">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -6439,7 +6528,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="3" customFormat="1" ht="12.8">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -6698,7 +6787,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" ht="12.8">
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -6947,7 +7036,7 @@
       <c r="IV120" s="1"/>
       <c r="IW120" s="1"/>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="12.8">
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
@@ -7196,7 +7285,7 @@
       <c r="IV121" s="1"/>
       <c r="IW121" s="1"/>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" ht="12.8">
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
@@ -7445,7 +7534,7 @@
       <c r="IV122" s="1"/>
       <c r="IW122" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" s="3" customFormat="1" ht="12.8">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7704,7 +7793,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" s="3" customFormat="1" ht="12.8">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7963,7 +8052,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" s="3" customFormat="1" ht="12.8">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -8222,7 +8311,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="3" customFormat="1" ht="12.8">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8481,7 +8570,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="3" customFormat="1" ht="12.8">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8740,7 +8829,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="12.8">
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
@@ -8989,7 +9078,7 @@
       <c r="IV131" s="1"/>
       <c r="IW131" s="1"/>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="12.8">
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
@@ -9238,7 +9327,7 @@
       <c r="IV132" s="1"/>
       <c r="IW132" s="1"/>
     </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" ht="12.8">
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
@@ -9487,7 +9576,7 @@
       <c r="IV133" s="1"/>
       <c r="IW133" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="3" customFormat="1" ht="12.8">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -9746,7 +9835,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" ht="12.8">
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
@@ -9995,7 +10084,7 @@
       <c r="IV159" s="1"/>
       <c r="IW159" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" s="3" customFormat="1" ht="12.8">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -10254,7 +10343,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="3" customFormat="1" ht="12.8">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -10513,7 +10602,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" ht="12.8">
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
@@ -10762,7 +10851,7 @@
       <c r="IV162" s="1"/>
       <c r="IW162" s="1"/>
     </row>
-    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" ht="12.8">
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="1"/>
@@ -11011,7 +11100,7 @@
       <c r="IV163" s="1"/>
       <c r="IW163" s="1"/>
     </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" ht="12.8">
       <c r="K164" s="1"/>
       <c r="L164" s="1"/>
       <c r="M164" s="1"/>
@@ -11260,7 +11349,7 @@
       <c r="IV164" s="1"/>
       <c r="IW164" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="3" customFormat="1" ht="12.8">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -11519,7 +11608,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" ht="12.8">
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
@@ -11768,7 +11857,7 @@
       <c r="IV238" s="1"/>
       <c r="IW238" s="1"/>
     </row>
-    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" ht="12.8">
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
@@ -12017,7 +12106,7 @@
       <c r="IV239" s="1"/>
       <c r="IW239" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="5" customFormat="1" ht="12.8">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -12276,7 +12365,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" ht="12.8">
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
@@ -12525,7 +12614,7 @@
       <c r="IV242" s="1"/>
       <c r="IW242" s="1"/>
     </row>
-    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" ht="12.8">
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
@@ -12774,7 +12863,7 @@
       <c r="IV243" s="1"/>
       <c r="IW243" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="1" ht="12.8">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -13033,7 +13122,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" ht="12.8">
       <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
@@ -13282,7 +13371,7 @@
       <c r="IV274" s="1"/>
       <c r="IW274" s="1"/>
     </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" ht="12.8">
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
@@ -13531,7 +13620,7 @@
       <c r="IV275" s="1"/>
       <c r="IW275" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="5" customFormat="1" ht="12.8">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -13790,7 +13879,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="1" ht="12.8">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -14049,7 +14138,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" ht="12.8">
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
@@ -14298,7 +14387,7 @@
       <c r="IV288" s="1"/>
       <c r="IW288" s="1"/>
     </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" ht="12.8">
       <c r="K289" s="1"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
@@ -14547,7 +14636,7 @@
       <c r="IV289" s="1"/>
       <c r="IW289" s="1"/>
     </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" ht="12.8">
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
@@ -14796,7 +14885,7 @@
       <c r="IV290" s="1"/>
       <c r="IW290" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="5" customFormat="1" ht="12.8">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -15055,7 +15144,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" ht="12.8">
       <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
@@ -15304,7 +15393,7 @@
       <c r="IV302" s="1"/>
       <c r="IW302" s="1"/>
     </row>
-    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" ht="12.8">
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
@@ -15553,7 +15642,7 @@
       <c r="IV303" s="1"/>
       <c r="IW303" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="3" customFormat="1" ht="12.8">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -15812,7 +15901,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" ht="12.8">
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
@@ -16061,7 +16150,7 @@
       <c r="IV308" s="1"/>
       <c r="IW308" s="1"/>
     </row>
-    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" ht="12.8">
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
@@ -16310,7 +16399,7 @@
       <c r="IV309" s="1"/>
       <c r="IW309" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="3" customFormat="1" ht="12.8">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -16569,7 +16658,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" ht="12.8">
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
@@ -16818,7 +16907,7 @@
       <c r="IV315" s="1"/>
       <c r="IW315" s="1"/>
     </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" ht="12.8">
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
@@ -17067,7 +17156,7 @@
       <c r="IV316" s="1"/>
       <c r="IW316" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="3" customFormat="1" ht="12.8">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -17326,7 +17415,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" ht="12.8">
       <c r="K339" s="1"/>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
@@ -17575,7 +17664,7 @@
       <c r="IV339" s="1"/>
       <c r="IW339" s="1"/>
     </row>
-    <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" ht="12.8">
       <c r="K340" s="1"/>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
@@ -17824,7 +17913,7 @@
       <c r="IV340" s="1"/>
       <c r="IW340" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="3" customFormat="1" ht="12.8">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -18083,7 +18172,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" ht="12.8">
       <c r="K350" s="1"/>
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
@@ -18332,7 +18421,7 @@
       <c r="IV350" s="1"/>
       <c r="IW350" s="1"/>
     </row>
-    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" ht="12.8">
       <c r="K351" s="1"/>
       <c r="L351" s="1"/>
       <c r="M351" s="1"/>
@@ -18581,7 +18670,7 @@
       <c r="IV351" s="1"/>
       <c r="IW351" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="5" customFormat="1" ht="12.8">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -18840,7 +18929,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="5" customFormat="1" ht="12.8">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -19099,7 +19188,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" ht="12.8">
       <c r="K356" s="1"/>
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
@@ -19348,7 +19437,7 @@
       <c r="IV356" s="1"/>
       <c r="IW356" s="1"/>
     </row>
-    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" ht="12.8">
       <c r="K357" s="1"/>
       <c r="L357" s="1"/>
       <c r="M357" s="1"/>
@@ -19597,7 +19686,7 @@
       <c r="IV357" s="1"/>
       <c r="IW357" s="1"/>
     </row>
-    <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" ht="12.8">
       <c r="K358" s="1"/>
       <c r="L358" s="1"/>
       <c r="M358" s="1"/>
@@ -19846,7 +19935,7 @@
       <c r="IV358" s="1"/>
       <c r="IW358" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="5" customFormat="1" ht="12.8">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -20105,7 +20194,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" ht="12.8">
       <c r="K368" s="1"/>
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
@@ -20354,7 +20443,7 @@
       <c r="IV368" s="1"/>
       <c r="IW368" s="1"/>
     </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" ht="12.8">
       <c r="K369" s="1"/>
       <c r="L369" s="1"/>
       <c r="M369" s="1"/>
@@ -20603,7 +20692,7 @@
       <c r="IV369" s="1"/>
       <c r="IW369" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="1" ht="12.8">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -20862,7 +20951,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" ht="12.8">
       <c r="K413" s="1"/>
       <c r="L413" s="1"/>
       <c r="M413" s="1"/>
@@ -21111,7 +21200,7 @@
       <c r="IV413" s="1"/>
       <c r="IW413" s="1"/>
     </row>
-    <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" ht="12.8">
       <c r="K414" s="1"/>
       <c r="L414" s="1"/>
       <c r="M414" s="1"/>
@@ -21360,7 +21449,7 @@
       <c r="IV414" s="1"/>
       <c r="IW414" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" s="3" customFormat="1" ht="12.8">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -21619,7 +21708,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="5" customFormat="1" ht="12.8">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -21878,7 +21967,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" ht="12.8">
       <c r="K417" s="1"/>
       <c r="L417" s="1"/>
       <c r="M417" s="1"/>
@@ -22127,7 +22216,7 @@
       <c r="IV417" s="1"/>
       <c r="IW417" s="1"/>
     </row>
-    <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" ht="12.8">
       <c r="K418" s="1"/>
       <c r="L418" s="1"/>
       <c r="M418" s="1"/>
@@ -22376,7 +22465,7 @@
       <c r="IV418" s="1"/>
       <c r="IW418" s="1"/>
     </row>
-    <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" ht="12.8">
       <c r="K419" s="1"/>
       <c r="L419" s="1"/>
       <c r="M419" s="1"/>
@@ -22625,7 +22714,7 @@
       <c r="IV419" s="1"/>
       <c r="IW419" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="1" ht="12.8">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -22884,7 +22973,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="1" ht="12.8">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -23143,7 +23232,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" ht="12.8">
       <c r="K431" s="1"/>
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
@@ -23392,7 +23481,7 @@
       <c r="IV431" s="1"/>
       <c r="IW431" s="1"/>
     </row>
-    <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" ht="12.8">
       <c r="K432" s="1"/>
       <c r="L432" s="1"/>
       <c r="M432" s="1"/>
@@ -23641,7 +23730,7 @@
       <c r="IV432" s="1"/>
       <c r="IW432" s="1"/>
     </row>
-    <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" ht="12.8">
       <c r="K433" s="1"/>
       <c r="L433" s="1"/>
       <c r="M433" s="1"/>
@@ -23890,7 +23979,7 @@
       <c r="IV433" s="1"/>
       <c r="IW433" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" s="3" customFormat="1" ht="12.8">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -24149,7 +24238,7 @@
       <c r="IV439" s="1"/>
       <c r="IW439" s="1"/>
     </row>
-    <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" ht="12.8">
       <c r="K441" s="1"/>
       <c r="L441" s="1"/>
       <c r="M441" s="1"/>
@@ -24398,7 +24487,7 @@
       <c r="IV441" s="1"/>
       <c r="IW441" s="1"/>
     </row>
-    <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" ht="12.8">
       <c r="K442" s="1"/>
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
@@ -24649,12 +24738,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -24662,24 +24751,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:IW439"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62.98"/>
+    <col min="1" max="1" width="12.51" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="62.12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="62.98" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24714,13 +24803,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -24728,14 +24817,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="1">
         <v>3</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -24744,8 +24833,11 @@
       <c r="J6" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="K6" t="s">
+        <v>123</v>
+      </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
@@ -24753,12 +24845,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -25007,20 +25099,20 @@
       <c r="IV10" s="1"/>
       <c r="IW10" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>37</v>
       </c>
@@ -25028,11 +25120,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="1">
         <v>123</v>
       </c>
       <c r="I15" s="4"/>
@@ -25285,11 +25377,11 @@
       <c r="IV15" s="1"/>
       <c r="IW15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="43.25">
       <c r="F16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
@@ -25298,7 +25390,9 @@
       <c r="J16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -25546,7 +25640,7 @@
       <c r="IV16" s="1"/>
       <c r="IW16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
         <v>61</v>
       </c>
@@ -25556,7 +25650,7 @@
       <c r="F17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="1">
         <v>2</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -25565,19 +25659,22 @@
       <c r="J17" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="K17" t="s">
+        <v>125</v>
+      </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="A19" s="1" t="s">
         <v>61</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>64</v>
       </c>
@@ -25587,24 +25684,24 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="A24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="D25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="D26" s="1" t="s">
         <v>66</v>
       </c>
@@ -25612,20 +25709,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="D27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="D29" s="1" t="s">
         <v>64</v>
       </c>
@@ -25633,7 +25730,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="D30" s="1" t="s">
         <v>71</v>
       </c>
@@ -25641,35 +25738,35 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="D31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="D32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="D33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="85.05">
       <c r="F34" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="1">
         <v>4</v>
       </c>
       <c r="I34" s="4" t="s">
@@ -25678,8 +25775,11 @@
       <c r="J34" s="4" t="s">
         <v>76</v>
       </c>
+      <c r="K34" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="D35" s="1" t="s">
         <v>73</v>
       </c>
@@ -25687,11 +25787,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="53.7">
       <c r="F36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="H36" s="1">
         <v>5</v>
       </c>
       <c r="I36" s="4" t="s">
@@ -25700,15 +25800,18 @@
       <c r="J36" s="4" t="s">
         <v>79</v>
       </c>
+      <c r="K36" t="s">
+        <v>127</v>
+      </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="B37" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="1">
         <v>6</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -25717,15 +25820,18 @@
       <c r="J37" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="K37" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="B38" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="H38" s="1">
         <v>7</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -25734,14 +25840,17 @@
       <c r="J38" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="K38" t="s">
+        <v>129</v>
+      </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="A41" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H42" s="1" t="n">
+    <row r="42" ht="12.8">
+      <c r="H42" s="1">
         <v>8</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -25750,16 +25859,19 @@
       <c r="J42" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="K42" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.8">
       <c r="D43" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="D44" s="1" t="s">
         <v>64</v>
       </c>
@@ -25767,17 +25879,17 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="D47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="A49" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="D50" s="1" t="s">
         <v>73</v>
       </c>
@@ -25785,11 +25897,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="53.7">
       <c r="F51" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="1">
         <v>9</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -25798,8 +25910,11 @@
       <c r="J51" s="4" t="s">
         <v>89</v>
       </c>
+      <c r="K51" t="s">
+        <v>130</v>
+      </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.8">
       <c r="D52" s="1" t="s">
         <v>73</v>
       </c>
@@ -25807,8 +25922,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H53" s="1" t="n">
+    <row r="53" ht="12.8">
+      <c r="H53" s="1">
         <v>10</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -25817,8 +25932,11 @@
       <c r="J53" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="K53" t="s">
+        <v>131</v>
+      </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="D54" s="1" t="s">
         <v>73</v>
       </c>
@@ -25826,11 +25944,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="43.25">
       <c r="F55" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="H55" s="1">
         <v>11</v>
       </c>
       <c r="I55" s="4" t="s">
@@ -25839,15 +25957,18 @@
       <c r="J55" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="K55" t="s">
+        <v>132</v>
+      </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="12.8">
       <c r="B56" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="1">
         <v>12</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -25856,15 +25977,18 @@
       <c r="J56" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="K56" t="s">
+        <v>133</v>
+      </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="12.8">
       <c r="B57" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="1">
         <v>13</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -25873,15 +25997,18 @@
       <c r="J57" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="K57" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.8">
       <c r="B58" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="1">
         <v>14</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -25890,15 +26017,18 @@
       <c r="J58" s="6" t="s">
         <v>102</v>
       </c>
+      <c r="K58" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="B59" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="1">
         <v>15</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -25907,8 +26037,11 @@
       <c r="J59" s="6" t="s">
         <v>104</v>
       </c>
+      <c r="K59" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="61" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="3" customFormat="1" ht="12.8">
       <c r="A61" s="1" t="s">
         <v>94</v>
       </c>
@@ -26169,8 +26302,8 @@
       <c r="IV61" s="1"/>
       <c r="IW61" s="1"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H62" s="1" t="n">
+    <row r="62" ht="12.8">
+      <c r="H62" s="1">
         <v>16</v>
       </c>
       <c r="I62" s="7" t="s">
@@ -26179,13 +26312,16 @@
       <c r="J62" s="6" t="s">
         <v>106</v>
       </c>
+      <c r="K62" t="s">
+        <v>137</v>
+      </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.8">
       <c r="B63" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="65" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="5" customFormat="1" ht="12.8">
       <c r="A65" s="1" t="s">
         <v>100</v>
       </c>
@@ -26446,8 +26582,8 @@
       <c r="IV65" s="1"/>
       <c r="IW65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+    <row r="66" ht="12.8">
+      <c r="H66" s="1">
         <v>17</v>
       </c>
       <c r="I66" s="7" t="s">
@@ -26456,18 +26592,21 @@
       <c r="J66" s="6" t="s">
         <v>109</v>
       </c>
+      <c r="K66" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
       <c r="B67" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="A70" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
       <c r="D71" s="1" t="s">
         <v>35</v>
       </c>
@@ -26475,16 +26614,16 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="12.8">
       <c r="D72" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="1">
         <v>1</v>
       </c>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.8">
       <c r="D73" s="1" t="s">
         <v>64</v>
       </c>
@@ -26493,16 +26632,16 @@
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.8">
       <c r="D74" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="1">
         <v>1</v>
       </c>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.8">
       <c r="D75" s="1" t="s">
         <v>64</v>
       </c>
@@ -26511,17 +26650,17 @@
       </c>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.8">
       <c r="B76" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.8">
       <c r="A79" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="12.8">
       <c r="B80" s="1" t="s">
         <v>114</v>
       </c>
@@ -26529,17 +26668,17 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="12.8">
       <c r="B81" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="12.8">
       <c r="A84" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="85" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="3" customFormat="1" ht="12.8">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -26547,7 +26686,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1" t="n">
+      <c r="H85" s="1">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -26556,7 +26695,9 @@
       <c r="J85" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K85" s="1"/>
+      <c r="K85" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
@@ -26804,12 +26945,12 @@
       <c r="IV85" s="1"/>
       <c r="IW85" s="1"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="12.8">
       <c r="B86" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="89" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="5" customFormat="1" ht="12.8">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -27068,7 +27209,7 @@
       <c r="IV89" s="1"/>
       <c r="IW89" s="1"/>
     </row>
-    <row r="99" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" s="5" customFormat="1" ht="12.8">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -27327,7 +27468,7 @@
       <c r="IV99" s="1"/>
       <c r="IW99" s="1"/>
     </row>
-    <row r="117" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" s="3" customFormat="1" ht="12.8">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -27586,7 +27727,7 @@
       <c r="IV117" s="1"/>
       <c r="IW117" s="1"/>
     </row>
-    <row r="118" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" s="3" customFormat="1" ht="12.8">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -27845,7 +27986,7 @@
       <c r="IV118" s="1"/>
       <c r="IW118" s="1"/>
     </row>
-    <row r="119" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="3" customFormat="1" ht="12.8">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -28104,7 +28245,7 @@
       <c r="IV119" s="1"/>
       <c r="IW119" s="1"/>
     </row>
-    <row r="126" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" s="3" customFormat="1" ht="12.8">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -28363,7 +28504,7 @@
       <c r="IV126" s="1"/>
       <c r="IW126" s="1"/>
     </row>
-    <row r="127" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" s="3" customFormat="1" ht="12.8">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -28622,7 +28763,7 @@
       <c r="IV127" s="1"/>
       <c r="IW127" s="1"/>
     </row>
-    <row r="128" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" s="3" customFormat="1" ht="12.8">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -28881,7 +29022,7 @@
       <c r="IV128" s="1"/>
       <c r="IW128" s="1"/>
     </row>
-    <row r="129" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="3" customFormat="1" ht="12.8">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -29140,7 +29281,7 @@
       <c r="IV129" s="1"/>
       <c r="IW129" s="1"/>
     </row>
-    <row r="130" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="3" customFormat="1" ht="12.8">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -29399,7 +29540,7 @@
       <c r="IV130" s="1"/>
       <c r="IW130" s="1"/>
     </row>
-    <row r="157" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="3" customFormat="1" ht="12.8">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -29658,7 +29799,7 @@
       <c r="IV157" s="1"/>
       <c r="IW157" s="1"/>
     </row>
-    <row r="160" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" s="3" customFormat="1" ht="12.8">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -29917,7 +30058,7 @@
       <c r="IV160" s="1"/>
       <c r="IW160" s="1"/>
     </row>
-    <row r="161" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="3" customFormat="1" ht="12.8">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -30176,7 +30317,7 @@
       <c r="IV161" s="1"/>
       <c r="IW161" s="1"/>
     </row>
-    <row r="236" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="3" customFormat="1" ht="12.8">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -30435,7 +30576,7 @@
       <c r="IV236" s="1"/>
       <c r="IW236" s="1"/>
     </row>
-    <row r="240" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="5" customFormat="1" ht="12.8">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -30694,7 +30835,7 @@
       <c r="IV240" s="1"/>
       <c r="IW240" s="1"/>
     </row>
-    <row r="272" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="5" customFormat="1" ht="12.8">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -30953,7 +31094,7 @@
       <c r="IV272" s="1"/>
       <c r="IW272" s="1"/>
     </row>
-    <row r="286" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="5" customFormat="1" ht="12.8">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -31212,7 +31353,7 @@
       <c r="IV286" s="1"/>
       <c r="IW286" s="1"/>
     </row>
-    <row r="287" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="5" customFormat="1" ht="12.8">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -31471,7 +31612,7 @@
       <c r="IV287" s="1"/>
       <c r="IW287" s="1"/>
     </row>
-    <row r="300" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="5" customFormat="1" ht="12.8">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -31730,7 +31871,7 @@
       <c r="IV300" s="1"/>
       <c r="IW300" s="1"/>
     </row>
-    <row r="306" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="3" customFormat="1" ht="12.8">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -31989,7 +32130,7 @@
       <c r="IV306" s="1"/>
       <c r="IW306" s="1"/>
     </row>
-    <row r="313" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="3" customFormat="1" ht="12.8">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -32248,7 +32389,7 @@
       <c r="IV313" s="1"/>
       <c r="IW313" s="1"/>
     </row>
-    <row r="337" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="3" customFormat="1" ht="12.8">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -32507,7 +32648,7 @@
       <c r="IV337" s="1"/>
       <c r="IW337" s="1"/>
     </row>
-    <row r="348" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="3" customFormat="1" ht="12.8">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -32766,7 +32907,7 @@
       <c r="IV348" s="1"/>
       <c r="IW348" s="1"/>
     </row>
-    <row r="354" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="5" customFormat="1" ht="12.8">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -33025,7 +33166,7 @@
       <c r="IV354" s="1"/>
       <c r="IW354" s="1"/>
     </row>
-    <row r="355" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="5" customFormat="1" ht="12.8">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -33284,7 +33425,7 @@
       <c r="IV355" s="1"/>
       <c r="IW355" s="1"/>
     </row>
-    <row r="366" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="5" customFormat="1" ht="12.8">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -33543,7 +33684,7 @@
       <c r="IV366" s="1"/>
       <c r="IW366" s="1"/>
     </row>
-    <row r="411" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="5" customFormat="1" ht="12.8">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -33802,7 +33943,7 @@
       <c r="IV411" s="1"/>
       <c r="IW411" s="1"/>
     </row>
-    <row r="415" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" s="3" customFormat="1" ht="12.8">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -34061,7 +34202,7 @@
       <c r="IV415" s="1"/>
       <c r="IW415" s="1"/>
     </row>
-    <row r="416" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="5" customFormat="1" ht="12.8">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -34320,7 +34461,7 @@
       <c r="IV416" s="1"/>
       <c r="IW416" s="1"/>
     </row>
-    <row r="429" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="5" customFormat="1" ht="12.8">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -34579,7 +34720,7 @@
       <c r="IV429" s="1"/>
       <c r="IW429" s="1"/>
     </row>
-    <row r="430" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="5" customFormat="1" ht="12.8">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -34838,7 +34979,7 @@
       <c r="IV430" s="1"/>
       <c r="IW430" s="1"/>
     </row>
-    <row r="439" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" s="3" customFormat="1" ht="12.8">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -35099,21 +35240,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H11 H14 H72:H1048576 H36:H70 H24:H34">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H23 H12:H13">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H71">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
